--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676872</v>
+        <v>119676878</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>845984</v>
+        <v>846139</v>
       </c>
       <c r="R2" t="n">
-        <v>7427463</v>
+        <v>7427476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,18 +753,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>7 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676878</v>
+        <v>119676867</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>846139</v>
+        <v>845971</v>
       </c>
       <c r="R3" t="n">
-        <v>7427476</v>
+        <v>7427292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676867</v>
+        <v>119676872</v>
       </c>
       <c r="B4" t="n">
-        <v>79511</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>845971</v>
+        <v>845984</v>
       </c>
       <c r="R4" t="n">
-        <v>7427292</v>
+        <v>7427463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,12 +961,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676877</v>
+        <v>119676869</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>79643</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>846117</v>
+        <v>845947</v>
       </c>
       <c r="R21" t="n">
-        <v>7427460</v>
+        <v>7427449</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676869</v>
+        <v>119676880</v>
       </c>
       <c r="B22" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2757,25 +2757,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>845947</v>
+        <v>846022</v>
       </c>
       <c r="R22" t="n">
-        <v>7427449</v>
+        <v>7427290</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676880</v>
+        <v>119676864</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>846022</v>
+        <v>845949</v>
       </c>
       <c r="R23" t="n">
-        <v>7427290</v>
+        <v>7427416</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676864</v>
+        <v>119676877</v>
       </c>
       <c r="B24" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>845949</v>
+        <v>846117</v>
       </c>
       <c r="R24" t="n">
-        <v>7427416</v>
+        <v>7427460</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676861</v>
+        <v>119676886</v>
       </c>
       <c r="B6" t="n">
-        <v>87406</v>
+        <v>82305</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>846015</v>
+        <v>846076</v>
       </c>
       <c r="R6" t="n">
-        <v>7427303</v>
+        <v>7427388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676886</v>
+        <v>119676861</v>
       </c>
       <c r="B7" t="n">
-        <v>82305</v>
+        <v>87406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>4412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>846076</v>
+        <v>846015</v>
       </c>
       <c r="R7" t="n">
-        <v>7427388</v>
+        <v>7427303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676862</v>
+        <v>119676881</v>
       </c>
       <c r="B13" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>846078</v>
+        <v>845991</v>
       </c>
       <c r="R13" t="n">
-        <v>7427415</v>
+        <v>7427259</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676881</v>
+        <v>119676883</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>845991</v>
+        <v>846071</v>
       </c>
       <c r="R14" t="n">
-        <v>7427259</v>
+        <v>7427391</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676883</v>
+        <v>119676862</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>846071</v>
+        <v>846078</v>
       </c>
       <c r="R15" t="n">
-        <v>7427391</v>
+        <v>7427415</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676878</v>
+        <v>119676865</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>846139</v>
+        <v>845995</v>
       </c>
       <c r="R2" t="n">
-        <v>7427476</v>
+        <v>7427271</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676872</v>
+        <v>119676866</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>845984</v>
+        <v>846084</v>
       </c>
       <c r="R4" t="n">
-        <v>7427463</v>
+        <v>7427407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,18 +957,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>7 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676882</v>
+        <v>119676875</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>845997</v>
+        <v>845961</v>
       </c>
       <c r="R5" t="n">
-        <v>7427296</v>
+        <v>7427461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676886</v>
+        <v>119676863</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>846076</v>
+        <v>846010</v>
       </c>
       <c r="R6" t="n">
-        <v>7427388</v>
+        <v>7427280</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676861</v>
+        <v>119676873</v>
       </c>
       <c r="B7" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>846015</v>
+        <v>845959</v>
       </c>
       <c r="R7" t="n">
-        <v>7427303</v>
+        <v>7427467</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,12 +1263,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676865</v>
+        <v>119676862</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1305,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>845995</v>
+        <v>846078</v>
       </c>
       <c r="R8" t="n">
-        <v>7427271</v>
+        <v>7427415</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676871</v>
+        <v>119676886</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,42 +1407,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>845958</v>
+        <v>846076</v>
       </c>
       <c r="R9" t="n">
-        <v>7427474</v>
+        <v>7427388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,18 +1473,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>38 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1511,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676885</v>
+        <v>119676860</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>87406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1513,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>4412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>846141</v>
+        <v>845967</v>
       </c>
       <c r="R10" t="n">
-        <v>7427470</v>
+        <v>7427415</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676890</v>
+        <v>119676874</v>
       </c>
       <c r="B11" t="n">
-        <v>79642</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,38 +1611,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>845969</v>
+        <v>845958</v>
       </c>
       <c r="R11" t="n">
-        <v>7427290</v>
+        <v>7427450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,12 +1681,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1,5 kvm</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1715,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676884</v>
+        <v>119676864</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1727,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>846078</v>
+        <v>845949</v>
       </c>
       <c r="R12" t="n">
-        <v>7427400</v>
+        <v>7427416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676881</v>
+        <v>119676885</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>845991</v>
+        <v>846141</v>
       </c>
       <c r="R13" t="n">
-        <v>7427259</v>
+        <v>7427470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676883</v>
+        <v>119676861</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>87406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>846071</v>
+        <v>846015</v>
       </c>
       <c r="R14" t="n">
-        <v>7427391</v>
+        <v>7427303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676862</v>
+        <v>119676881</v>
       </c>
       <c r="B15" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2029,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>846078</v>
+        <v>845991</v>
       </c>
       <c r="R15" t="n">
-        <v>7427415</v>
+        <v>7427259</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676887</v>
+        <v>119676879</v>
       </c>
       <c r="B16" t="n">
-        <v>97824</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2131,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>845955</v>
+        <v>846121</v>
       </c>
       <c r="R16" t="n">
-        <v>7427457</v>
+        <v>7427477</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676868</v>
+        <v>119676883</v>
       </c>
       <c r="B17" t="n">
-        <v>96862</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2233,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>845916</v>
+        <v>846071</v>
       </c>
       <c r="R17" t="n">
-        <v>7427462</v>
+        <v>7427391</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676879</v>
+        <v>119676869</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2335,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2363,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>846121</v>
+        <v>845947</v>
       </c>
       <c r="R18" t="n">
-        <v>7427477</v>
+        <v>7427449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,7 +2425,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676874</v>
+        <v>119676876</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2463,20 +2459,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>845958</v>
+        <v>845949</v>
       </c>
       <c r="R19" t="n">
-        <v>7427450</v>
+        <v>7427453</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,18 +2503,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1,5 kvm</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2541,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676866</v>
+        <v>119676890</v>
       </c>
       <c r="B20" t="n">
-        <v>57326</v>
+        <v>79642</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,25 +2539,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>846084</v>
+        <v>845969</v>
       </c>
       <c r="R20" t="n">
-        <v>7427407</v>
+        <v>7427290</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676869</v>
+        <v>119676894</v>
       </c>
       <c r="B21" t="n">
-        <v>79643</v>
+        <v>91228</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>898</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>845947</v>
+        <v>846123</v>
       </c>
       <c r="R21" t="n">
-        <v>7427449</v>
+        <v>7427452</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,6 +2713,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2745,7 +2732,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676880</v>
+        <v>119676884</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2785,10 +2772,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>846022</v>
+        <v>846078</v>
       </c>
       <c r="R22" t="n">
-        <v>7427290</v>
+        <v>7427400</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2847,10 +2834,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676864</v>
+        <v>119676877</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2850,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2874,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>845949</v>
+        <v>846117</v>
       </c>
       <c r="R23" t="n">
-        <v>7427416</v>
+        <v>7427460</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2949,10 +2936,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676877</v>
+        <v>119676871</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2961,38 +2948,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>846117</v>
+        <v>845958</v>
       </c>
       <c r="R24" t="n">
-        <v>7427460</v>
+        <v>7427474</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3027,12 +3018,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>38 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3051,10 +3048,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676863</v>
+        <v>119676872</v>
       </c>
       <c r="B25" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3063,38 +3060,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>846010</v>
+        <v>845984</v>
       </c>
       <c r="R25" t="n">
-        <v>7427280</v>
+        <v>7427463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,12 +3130,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3153,10 +3160,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676875</v>
+        <v>119676882</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3165,25 +3172,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3193,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>845961</v>
+        <v>845997</v>
       </c>
       <c r="R26" t="n">
-        <v>7427461</v>
+        <v>7427296</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3255,10 +3262,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676888</v>
+        <v>119676878</v>
       </c>
       <c r="B27" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3267,20 +3274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3295,10 +3302,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>845940</v>
+        <v>846139</v>
       </c>
       <c r="R27" t="n">
-        <v>7427386</v>
+        <v>7427476</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676894</v>
+        <v>119676868</v>
       </c>
       <c r="B28" t="n">
-        <v>91228</v>
+        <v>96862</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3369,25 +3376,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>898</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3397,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>846123</v>
+        <v>845916</v>
       </c>
       <c r="R28" t="n">
-        <v>7427452</v>
+        <v>7427462</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,7 +3448,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3460,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676876</v>
+        <v>119676880</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3472,25 +3478,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3500,10 +3506,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>845949</v>
+        <v>846022</v>
       </c>
       <c r="R29" t="n">
-        <v>7427453</v>
+        <v>7427290</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3562,10 +3568,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676873</v>
+        <v>119676888</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3574,25 +3580,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3602,10 +3608,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>845959</v>
+        <v>845940</v>
       </c>
       <c r="R30" t="n">
-        <v>7427467</v>
+        <v>7427386</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,18 +3646,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119676860</v>
+        <v>119676887</v>
       </c>
       <c r="B31" t="n">
-        <v>87406</v>
+        <v>97824</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3682,25 +3682,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4412</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>845967</v>
+        <v>845955</v>
       </c>
       <c r="R31" t="n">
-        <v>7427415</v>
+        <v>7427457</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676862</v>
+        <v>119676860</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>87406</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>4412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>846078</v>
+        <v>845967</v>
       </c>
       <c r="R8" t="n">
         <v>7427415</v>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676886</v>
+        <v>119676862</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,25 +1407,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>846076</v>
+        <v>846078</v>
       </c>
       <c r="R9" t="n">
-        <v>7427388</v>
+        <v>7427415</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676860</v>
+        <v>119676886</v>
       </c>
       <c r="B10" t="n">
-        <v>87406</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,21 +1513,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4412</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>845967</v>
+        <v>846076</v>
       </c>
       <c r="R10" t="n">
-        <v>7427415</v>
+        <v>7427388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676865</v>
+        <v>119676878</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>845995</v>
+        <v>846139</v>
       </c>
       <c r="R2" t="n">
-        <v>7427271</v>
+        <v>7427476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676867</v>
+        <v>119676866</v>
       </c>
       <c r="B3" t="n">
-        <v>79511</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>845971</v>
+        <v>846084</v>
       </c>
       <c r="R3" t="n">
-        <v>7427292</v>
+        <v>7427407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676866</v>
+        <v>119676874</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>846084</v>
+        <v>845958</v>
       </c>
       <c r="R4" t="n">
-        <v>7427407</v>
+        <v>7427450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +961,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1,5 kvm</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676875</v>
+        <v>119676860</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>845961</v>
+        <v>845967</v>
       </c>
       <c r="R5" t="n">
-        <v>7427461</v>
+        <v>7427415</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676863</v>
+        <v>119676879</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>846010</v>
+        <v>846121</v>
       </c>
       <c r="R6" t="n">
-        <v>7427280</v>
+        <v>7427477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676873</v>
+        <v>119676888</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>79642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>845959</v>
+        <v>845940</v>
       </c>
       <c r="R7" t="n">
-        <v>7427467</v>
+        <v>7427386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,18 +1273,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1293,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676860</v>
+        <v>119676890</v>
       </c>
       <c r="B8" t="n">
-        <v>87406</v>
+        <v>79642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4412</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1333,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>845967</v>
+        <v>845969</v>
       </c>
       <c r="R8" t="n">
-        <v>7427415</v>
+        <v>7427290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676862</v>
+        <v>119676863</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1435,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>846078</v>
+        <v>846010</v>
       </c>
       <c r="R9" t="n">
-        <v>7427415</v>
+        <v>7427280</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676886</v>
+        <v>119676875</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1509,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1537,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>846076</v>
+        <v>845961</v>
       </c>
       <c r="R10" t="n">
-        <v>7427388</v>
+        <v>7427461</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676874</v>
+        <v>119676884</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1611,42 +1615,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>845958</v>
+        <v>846078</v>
       </c>
       <c r="R11" t="n">
-        <v>7427450</v>
+        <v>7427400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,18 +1681,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1,5 kvm</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676864</v>
+        <v>119676867</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>79511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>845949</v>
+        <v>845971</v>
       </c>
       <c r="R12" t="n">
-        <v>7427416</v>
+        <v>7427292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676885</v>
+        <v>119676876</v>
       </c>
       <c r="B13" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1825,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>846141</v>
+        <v>845949</v>
       </c>
       <c r="R13" t="n">
-        <v>7427470</v>
+        <v>7427453</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676861</v>
+        <v>119676869</v>
       </c>
       <c r="B14" t="n">
-        <v>87406</v>
+        <v>79643</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4412</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>846015</v>
+        <v>845947</v>
       </c>
       <c r="R14" t="n">
-        <v>7427303</v>
+        <v>7427449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676881</v>
+        <v>119676887</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>97824</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2029,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>845991</v>
+        <v>845955</v>
       </c>
       <c r="R15" t="n">
-        <v>7427259</v>
+        <v>7427457</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676879</v>
+        <v>119676872</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2131,38 +2125,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>846121</v>
+        <v>845984</v>
       </c>
       <c r="R16" t="n">
-        <v>7427477</v>
+        <v>7427463</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,12 +2195,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2221,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676883</v>
+        <v>119676861</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>87406</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>846071</v>
+        <v>846015</v>
       </c>
       <c r="R17" t="n">
-        <v>7427391</v>
+        <v>7427303</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676869</v>
+        <v>119676864</v>
       </c>
       <c r="B18" t="n">
-        <v>79643</v>
+        <v>57326</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>845947</v>
+        <v>845949</v>
       </c>
       <c r="R18" t="n">
-        <v>7427449</v>
+        <v>7427416</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676876</v>
+        <v>119676877</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2437,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>845949</v>
+        <v>846117</v>
       </c>
       <c r="R19" t="n">
-        <v>7427453</v>
+        <v>7427460</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676890</v>
+        <v>119676871</v>
       </c>
       <c r="B20" t="n">
-        <v>79642</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2539,38 +2543,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>845969</v>
+        <v>845958</v>
       </c>
       <c r="R20" t="n">
-        <v>7427290</v>
+        <v>7427474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,12 +2613,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>38 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2629,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676894</v>
+        <v>119676868</v>
       </c>
       <c r="B21" t="n">
-        <v>91228</v>
+        <v>96862</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>898</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>846123</v>
+        <v>845916</v>
       </c>
       <c r="R21" t="n">
-        <v>7427452</v>
+        <v>7427462</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2727,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2732,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676884</v>
+        <v>119676873</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2744,25 +2757,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2772,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>846078</v>
+        <v>845959</v>
       </c>
       <c r="R22" t="n">
-        <v>7427400</v>
+        <v>7427467</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,12 +2823,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2834,10 +2853,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676877</v>
+        <v>119676865</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2850,21 +2869,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2874,10 +2893,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>846117</v>
+        <v>845995</v>
       </c>
       <c r="R23" t="n">
-        <v>7427460</v>
+        <v>7427271</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2936,10 +2955,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676871</v>
+        <v>119676885</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2948,42 +2967,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>845958</v>
+        <v>846141</v>
       </c>
       <c r="R24" t="n">
-        <v>7427474</v>
+        <v>7427470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,18 +3033,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>38 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3048,10 +3057,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676872</v>
+        <v>119676883</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3060,42 +3069,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>845984</v>
+        <v>846071</v>
       </c>
       <c r="R25" t="n">
-        <v>7427463</v>
+        <v>7427391</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,18 +3135,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>7 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3262,7 +3261,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676878</v>
+        <v>119676880</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3302,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>846139</v>
+        <v>846022</v>
       </c>
       <c r="R27" t="n">
-        <v>7427476</v>
+        <v>7427290</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,10 +3363,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676868</v>
+        <v>119676886</v>
       </c>
       <c r="B28" t="n">
-        <v>96862</v>
+        <v>82305</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3376,25 +3375,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3403,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>845916</v>
+        <v>846076</v>
       </c>
       <c r="R28" t="n">
-        <v>7427462</v>
+        <v>7427388</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,10 +3465,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676880</v>
+        <v>119676862</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>90527</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3478,25 +3477,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3506,10 +3505,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>846022</v>
+        <v>846078</v>
       </c>
       <c r="R29" t="n">
-        <v>7427290</v>
+        <v>7427415</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3568,10 +3567,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676888</v>
+        <v>119676881</v>
       </c>
       <c r="B30" t="n">
-        <v>79642</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3580,20 +3579,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3608,10 +3607,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>845940</v>
+        <v>845991</v>
       </c>
       <c r="R30" t="n">
-        <v>7427386</v>
+        <v>7427259</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3670,10 +3669,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119676887</v>
+        <v>119676894</v>
       </c>
       <c r="B31" t="n">
-        <v>97824</v>
+        <v>91228</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3682,25 +3681,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3710,10 +3709,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>845955</v>
+        <v>846123</v>
       </c>
       <c r="R31" t="n">
-        <v>7427457</v>
+        <v>7427452</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3754,6 +3753,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676878</v>
+        <v>119676887</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>97824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>846139</v>
+        <v>845955</v>
       </c>
       <c r="R2" t="n">
-        <v>7427476</v>
+        <v>7427457</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676866</v>
+        <v>119676865</v>
       </c>
       <c r="B3" t="n">
         <v>57326</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>846084</v>
+        <v>845995</v>
       </c>
       <c r="R3" t="n">
-        <v>7427407</v>
+        <v>7427271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676874</v>
+        <v>119676880</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>845958</v>
+        <v>846022</v>
       </c>
       <c r="R4" t="n">
-        <v>7427450</v>
+        <v>7427290</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,18 +957,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1,5 kvm</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676860</v>
+        <v>119676884</v>
       </c>
       <c r="B5" t="n">
-        <v>87406</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>845967</v>
+        <v>846078</v>
       </c>
       <c r="R5" t="n">
-        <v>7427415</v>
+        <v>7427400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676879</v>
+        <v>119676861</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>87406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>846121</v>
+        <v>846015</v>
       </c>
       <c r="R6" t="n">
-        <v>7427477</v>
+        <v>7427303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676888</v>
+        <v>119676872</v>
       </c>
       <c r="B7" t="n">
-        <v>79642</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1197,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>845940</v>
+        <v>845984</v>
       </c>
       <c r="R7" t="n">
-        <v>7427386</v>
+        <v>7427463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,12 +1267,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676890</v>
+        <v>119676863</v>
       </c>
       <c r="B8" t="n">
-        <v>79642</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>845969</v>
+        <v>846010</v>
       </c>
       <c r="R8" t="n">
-        <v>7427290</v>
+        <v>7427280</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676863</v>
+        <v>119676885</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>82305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>846010</v>
+        <v>846141</v>
       </c>
       <c r="R9" t="n">
-        <v>7427280</v>
+        <v>7427470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676875</v>
+        <v>119676869</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>845961</v>
+        <v>845947</v>
       </c>
       <c r="R10" t="n">
-        <v>7427461</v>
+        <v>7427449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676884</v>
+        <v>119676874</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1615,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>846078</v>
+        <v>845958</v>
       </c>
       <c r="R11" t="n">
-        <v>7427400</v>
+        <v>7427450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,12 +1685,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1,5 kvm</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676867</v>
+        <v>119676886</v>
       </c>
       <c r="B12" t="n">
-        <v>79511</v>
+        <v>82305</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>845971</v>
+        <v>846076</v>
       </c>
       <c r="R12" t="n">
-        <v>7427292</v>
+        <v>7427388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676876</v>
+        <v>119676883</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>845949</v>
+        <v>846071</v>
       </c>
       <c r="R13" t="n">
-        <v>7427453</v>
+        <v>7427391</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676869</v>
+        <v>119676881</v>
       </c>
       <c r="B14" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>845947</v>
+        <v>845991</v>
       </c>
       <c r="R14" t="n">
-        <v>7427449</v>
+        <v>7427259</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676887</v>
+        <v>119676867</v>
       </c>
       <c r="B15" t="n">
-        <v>97824</v>
+        <v>79511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>845955</v>
+        <v>845971</v>
       </c>
       <c r="R15" t="n">
-        <v>7427457</v>
+        <v>7427292</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676872</v>
+        <v>119676873</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2146,21 +2156,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>845984</v>
+        <v>845959</v>
       </c>
       <c r="R16" t="n">
-        <v>7427463</v>
+        <v>7427467</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,7 +2203,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>7 bladrosetter</t>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676861</v>
+        <v>119676879</v>
       </c>
       <c r="B17" t="n">
-        <v>87406</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2247,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4412</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2271,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>846015</v>
+        <v>846121</v>
       </c>
       <c r="R17" t="n">
-        <v>7427303</v>
+        <v>7427477</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676864</v>
+        <v>119676882</v>
       </c>
       <c r="B18" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2349,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>845949</v>
+        <v>845997</v>
       </c>
       <c r="R18" t="n">
-        <v>7427416</v>
+        <v>7427296</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676877</v>
+        <v>119676864</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>57326</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2451,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>846117</v>
+        <v>845949</v>
       </c>
       <c r="R19" t="n">
-        <v>7427460</v>
+        <v>7427416</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,7 +2537,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676871</v>
+        <v>119676875</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2564,21 +2570,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>845958</v>
+        <v>845961</v>
       </c>
       <c r="R20" t="n">
-        <v>7427474</v>
+        <v>7427461</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,18 +2615,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>38 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2643,10 +2639,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676868</v>
+        <v>119676877</v>
       </c>
       <c r="B21" t="n">
-        <v>96862</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2651,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2679,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>845916</v>
+        <v>846117</v>
       </c>
       <c r="R21" t="n">
-        <v>7427462</v>
+        <v>7427460</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,10 +2741,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676873</v>
+        <v>119676866</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2757,25 +2753,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2781,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>845959</v>
+        <v>846084</v>
       </c>
       <c r="R22" t="n">
-        <v>7427467</v>
+        <v>7427407</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,18 +2819,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2853,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676865</v>
+        <v>119676860</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>87406</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2869,21 +2859,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2893,10 +2883,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>845995</v>
+        <v>845967</v>
       </c>
       <c r="R23" t="n">
-        <v>7427271</v>
+        <v>7427415</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2955,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676885</v>
+        <v>119676876</v>
       </c>
       <c r="B24" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2967,25 +2957,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2995,10 +2985,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>846141</v>
+        <v>845949</v>
       </c>
       <c r="R24" t="n">
-        <v>7427470</v>
+        <v>7427453</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3057,7 +3047,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676883</v>
+        <v>119676878</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3097,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>846071</v>
+        <v>846139</v>
       </c>
       <c r="R25" t="n">
-        <v>7427391</v>
+        <v>7427476</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3159,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676882</v>
+        <v>119676894</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>91228</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3171,25 +3161,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3199,10 +3189,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>845997</v>
+        <v>846123</v>
       </c>
       <c r="R26" t="n">
-        <v>7427296</v>
+        <v>7427452</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,6 +3233,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3261,10 +3252,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676880</v>
+        <v>119676871</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3273,38 +3264,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>846022</v>
+        <v>845958</v>
       </c>
       <c r="R27" t="n">
-        <v>7427290</v>
+        <v>7427474</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3339,12 +3334,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>38 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3363,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676886</v>
+        <v>119676862</v>
       </c>
       <c r="B28" t="n">
-        <v>82305</v>
+        <v>90527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3375,25 +3376,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3403,10 +3404,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>846076</v>
+        <v>846078</v>
       </c>
       <c r="R28" t="n">
-        <v>7427388</v>
+        <v>7427415</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3465,10 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676862</v>
+        <v>119676890</v>
       </c>
       <c r="B29" t="n">
-        <v>90527</v>
+        <v>79642</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3481,21 +3482,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3505,10 +3506,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>846078</v>
+        <v>845969</v>
       </c>
       <c r="R29" t="n">
-        <v>7427415</v>
+        <v>7427290</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3567,10 +3568,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676881</v>
+        <v>119676888</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>79642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3579,20 +3580,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3607,10 +3608,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>845991</v>
+        <v>845940</v>
       </c>
       <c r="R30" t="n">
-        <v>7427259</v>
+        <v>7427386</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,10 +3670,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119676894</v>
+        <v>119676868</v>
       </c>
       <c r="B31" t="n">
-        <v>91228</v>
+        <v>96862</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3681,25 +3682,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3709,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>846123</v>
+        <v>845916</v>
       </c>
       <c r="R31" t="n">
-        <v>7427452</v>
+        <v>7427462</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3753,7 +3754,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676887</v>
+        <v>119676865</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>845955</v>
+        <v>845995</v>
       </c>
       <c r="R2" t="n">
-        <v>7427457</v>
+        <v>7427271</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676865</v>
+        <v>119676887</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>97824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>845995</v>
+        <v>845955</v>
       </c>
       <c r="R3" t="n">
-        <v>7427271</v>
+        <v>7427457</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676865</v>
+        <v>119676887</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>97824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>845995</v>
+        <v>845955</v>
       </c>
       <c r="R2" t="n">
-        <v>7427271</v>
+        <v>7427457</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676887</v>
+        <v>119676865</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>845955</v>
+        <v>845995</v>
       </c>
       <c r="R3" t="n">
-        <v>7427457</v>
+        <v>7427271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676864</v>
+        <v>119676875</v>
       </c>
       <c r="B19" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,25 +2447,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>845949</v>
+        <v>845961</v>
       </c>
       <c r="R19" t="n">
-        <v>7427416</v>
+        <v>7427461</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676875</v>
+        <v>119676864</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2549,25 +2549,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>845961</v>
+        <v>845949</v>
       </c>
       <c r="R20" t="n">
-        <v>7427461</v>
+        <v>7427416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676878</v>
+        <v>119676894</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>91228</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3059,25 +3059,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>846139</v>
+        <v>846123</v>
       </c>
       <c r="R25" t="n">
-        <v>7427476</v>
+        <v>7427452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3131,6 +3131,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3149,10 +3150,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676894</v>
+        <v>119676878</v>
       </c>
       <c r="B26" t="n">
-        <v>91228</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3161,25 +3162,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3189,10 +3190,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>846123</v>
+        <v>846139</v>
       </c>
       <c r="R26" t="n">
-        <v>7427452</v>
+        <v>7427476</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,7 +3234,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676886</v>
+        <v>119676883</v>
       </c>
       <c r="B12" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>846076</v>
+        <v>846071</v>
       </c>
       <c r="R12" t="n">
-        <v>7427388</v>
+        <v>7427391</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676883</v>
+        <v>119676886</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>846071</v>
+        <v>846076</v>
       </c>
       <c r="R13" t="n">
-        <v>7427391</v>
+        <v>7427388</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676883</v>
+        <v>119676886</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>846071</v>
+        <v>846076</v>
       </c>
       <c r="R12" t="n">
-        <v>7427391</v>
+        <v>7427388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676886</v>
+        <v>119676883</v>
       </c>
       <c r="B13" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>846076</v>
+        <v>846071</v>
       </c>
       <c r="R13" t="n">
-        <v>7427388</v>
+        <v>7427391</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676875</v>
+        <v>119676864</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,25 +2447,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>845961</v>
+        <v>845949</v>
       </c>
       <c r="R19" t="n">
-        <v>7427461</v>
+        <v>7427416</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676864</v>
+        <v>119676875</v>
       </c>
       <c r="B20" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2549,25 +2549,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>845949</v>
+        <v>845961</v>
       </c>
       <c r="R20" t="n">
-        <v>7427416</v>
+        <v>7427461</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676887</v>
+        <v>119676894</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>845955</v>
+        <v>846123</v>
       </c>
       <c r="R2" t="n">
-        <v>7427457</v>
+        <v>7427452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +754,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676865</v>
+        <v>119676885</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>845995</v>
+        <v>846141</v>
       </c>
       <c r="R3" t="n">
-        <v>7427271</v>
+        <v>7427470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676880</v>
+        <v>119676886</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>846022</v>
+        <v>846076</v>
       </c>
       <c r="R4" t="n">
-        <v>7427290</v>
+        <v>7427388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676884</v>
+        <v>119676860</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>846078</v>
+        <v>845967</v>
       </c>
       <c r="R5" t="n">
-        <v>7427400</v>
+        <v>7427415</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,12 +1067,7 @@
         <v>119676861</v>
       </c>
       <c r="B6" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,54 +1161,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676872</v>
+        <v>119676862</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>845984</v>
+        <v>846078</v>
       </c>
       <c r="R7" t="n">
-        <v>7427463</v>
+        <v>7427415</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,18 +1234,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>7 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676863</v>
+        <v>119676878</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>846010</v>
+        <v>846139</v>
       </c>
       <c r="R8" t="n">
-        <v>7427280</v>
+        <v>7427476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,37 +1355,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676885</v>
+        <v>119676879</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>846141</v>
+        <v>846121</v>
       </c>
       <c r="R9" t="n">
-        <v>7427470</v>
+        <v>7427477</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,37 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676869</v>
+        <v>119676880</v>
       </c>
       <c r="B10" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>845947</v>
+        <v>846022</v>
       </c>
       <c r="R10" t="n">
-        <v>7427449</v>
+        <v>7427290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,15 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676874</v>
+        <v>119676881</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,38 +1560,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>845958</v>
+        <v>845991</v>
       </c>
       <c r="R11" t="n">
-        <v>7427450</v>
+        <v>7427259</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,18 +1622,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1,5 kvm</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1715,37 +1646,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119676886</v>
+        <v>119676882</v>
       </c>
       <c r="B12" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>846076</v>
+        <v>845997</v>
       </c>
       <c r="R12" t="n">
-        <v>7427388</v>
+        <v>7427296</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,16 +1746,11 @@
         <v>119676883</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1919,19 +1840,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676881</v>
+        <v>119676884</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1959,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>845991</v>
+        <v>846078</v>
       </c>
       <c r="R14" t="n">
-        <v>7427259</v>
+        <v>7427400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,12 +1940,7 @@
         <v>119676867</v>
       </c>
       <c r="B15" t="n">
-        <v>79511</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,37 +2034,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676873</v>
+        <v>119676888</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>845959</v>
+        <v>845940</v>
       </c>
       <c r="R16" t="n">
-        <v>7427467</v>
+        <v>7427386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,18 +2107,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2231,32 +2131,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676879</v>
+        <v>119676890</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2271,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>846121</v>
+        <v>845969</v>
       </c>
       <c r="R17" t="n">
-        <v>7427477</v>
+        <v>7427290</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2333,37 +2228,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676882</v>
+        <v>119676869</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2373,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>845997</v>
+        <v>845947</v>
       </c>
       <c r="R18" t="n">
-        <v>7427296</v>
+        <v>7427449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,16 +2328,11 @@
         <v>119676864</v>
       </c>
       <c r="B19" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2537,37 +2422,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676875</v>
+        <v>119676865</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>845961</v>
+        <v>845995</v>
       </c>
       <c r="R20" t="n">
-        <v>7427461</v>
+        <v>7427271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,37 +2519,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676877</v>
+        <v>119676866</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2679,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>846117</v>
+        <v>846084</v>
       </c>
       <c r="R21" t="n">
-        <v>7427460</v>
+        <v>7427407</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2741,15 +2616,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676866</v>
+        <v>119676863</v>
       </c>
       <c r="B22" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2757,21 +2627,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2781,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>846084</v>
+        <v>846010</v>
       </c>
       <c r="R22" t="n">
-        <v>7427407</v>
+        <v>7427280</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2843,37 +2713,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676860</v>
+        <v>119676887</v>
       </c>
       <c r="B23" t="n">
-        <v>87406</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2883,10 +2748,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>845967</v>
+        <v>845955</v>
       </c>
       <c r="R23" t="n">
-        <v>7427415</v>
+        <v>7427457</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,15 +2810,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676876</v>
+        <v>119676871</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2978,17 +2838,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>845949</v>
+        <v>845958</v>
       </c>
       <c r="R24" t="n">
-        <v>7427453</v>
+        <v>7427474</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,12 +2887,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>38 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3047,15 +2917,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676894</v>
+        <v>119676872</v>
       </c>
       <c r="B25" t="n">
-        <v>91228</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,34 +2928,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>846123</v>
+        <v>845984</v>
       </c>
       <c r="R25" t="n">
-        <v>7427452</v>
+        <v>7427463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,6 +2992,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>7 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3150,37 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119676878</v>
+        <v>119676873</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3190,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>846139</v>
+        <v>845959</v>
       </c>
       <c r="R26" t="n">
-        <v>7427476</v>
+        <v>7427467</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3228,12 +3097,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3252,15 +3127,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119676871</v>
+        <v>119676874</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3285,11 +3155,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Salmi, Nb</t>
@@ -3299,7 +3169,7 @@
         <v>845958</v>
       </c>
       <c r="R27" t="n">
-        <v>7427474</v>
+        <v>7427450</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,7 +3206,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>38 bladrosetter</t>
+          <t>1,5 kvm</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3364,37 +3234,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119676862</v>
+        <v>119676875</v>
       </c>
       <c r="B28" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3404,10 +3269,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>846078</v>
+        <v>845961</v>
       </c>
       <c r="R28" t="n">
-        <v>7427415</v>
+        <v>7427461</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,37 +3331,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119676890</v>
+        <v>119676876</v>
       </c>
       <c r="B29" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3506,10 +3366,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>845969</v>
+        <v>845949</v>
       </c>
       <c r="R29" t="n">
-        <v>7427290</v>
+        <v>7427453</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3568,15 +3428,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119676888</v>
+        <v>119676868</v>
       </c>
       <c r="B30" t="n">
-        <v>79642</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3584,21 +3439,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3608,10 +3463,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>845940</v>
+        <v>845916</v>
       </c>
       <c r="R30" t="n">
-        <v>7427386</v>
+        <v>7427462</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3667,108 +3522,6 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>119676868</v>
-      </c>
-      <c r="B31" t="n">
-        <v>96862</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Salmi, Nb</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>845916</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7427462</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Korpilombolo</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16240-2024 artfynd.xlsx
+++ b/artfynd/A 16240-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676894</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676885</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676886</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676860</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676861</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676862</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676878</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676879</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676880</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676881</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676882</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676883</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676884</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676867</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676888</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676890</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676869</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676864</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2516,6 +2611,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676865</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2613,6 +2713,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676866</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676863</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676887</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2914,6 +3029,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676871</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3021,6 +3141,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676872</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3124,6 +3249,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676873</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3231,6 +3361,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676874</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3328,6 +3463,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676875</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3425,6 +3565,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676876</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3522,8 +3667,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119676868</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>